--- a/TitanSiege/Data/Excel/NPC配置表.xlsx
+++ b/TitanSiege/Data/Excel/NPC配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26148" windowHeight="13620"/>
+    <workbookView windowWidth="23040" windowHeight="9300"/>
   </bookViews>
   <sheets>
     <sheet name="NPC配置表" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t>UIRes/head/longnv.png</t>
+  </si>
+  <si>
+    <t>红鬃野狼</t>
+  </si>
+  <si>
+    <t>101|102</t>
+  </si>
+  <si>
+    <t>NPCPrefab/lang2.prefab</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1085,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="17" width="9.13888888888889" customWidth="1"/>
     <col min="18" max="18" width="9.93518518518519" customWidth="1"/>
@@ -1371,6 +1380,69 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:21">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>600</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>20</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/TitanSiege/Data/Excel/NPC配置表.xlsx
+++ b/TitanSiege/Data/Excel/NPC配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9300"/>
+    <workbookView windowWidth="30048" windowHeight="13620"/>
   </bookViews>
   <sheets>
     <sheet name="NPC配置表" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -28,6 +28,9 @@
     <t>等级</t>
   </si>
   <si>
+    <t>升级系数</t>
+  </si>
+  <si>
     <t>经验</t>
   </si>
   <si>
@@ -86,12 +89,6 @@
   </si>
   <si>
     <t>人族剑士</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>无名菜鸟</t>
@@ -152,15 +149,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -618,48 +610,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -669,103 +664,99 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1085,18 +1076,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="17" width="9.13888888888889" customWidth="1"/>
-    <col min="18" max="18" width="9.93518518518519" customWidth="1"/>
-    <col min="19" max="20" width="9.13888888888889" customWidth="1"/>
-    <col min="21" max="21" width="22.1111111111111" customWidth="1"/>
-    <col min="22" max="22" width="17.2962962962963" customWidth="1"/>
-    <col min="23" max="23" width="24.2592592592593" customWidth="1"/>
+    <col min="1" max="4" width="9.13888888888889" customWidth="1"/>
+    <col min="5" max="5" width="9.51851851851852" customWidth="1"/>
+    <col min="6" max="18" width="9.13888888888889" customWidth="1"/>
+    <col min="19" max="19" width="9.51851851851852" customWidth="1"/>
+    <col min="20" max="21" width="9.13888888888889" customWidth="1"/>
+    <col min="22" max="22" width="21.3611111111111" customWidth="1"/>
+    <col min="23" max="23" width="16.6759259259259" customWidth="1"/>
+    <col min="24" max="24" width="23.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1166,44 +1159,47 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>500</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>100</v>
-      </c>
-      <c r="H2">
-        <v>8</v>
       </c>
       <c r="I2">
         <v>8</v>
       </c>
       <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
       <c r="M2">
         <v>0</v>
       </c>
@@ -1214,138 +1210,144 @@
         <v>0</v>
       </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>500</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>100</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>27</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>28</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>29</v>
       </c>
-      <c r="W2" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
+      <c r="B3" t="s">
+        <v>30</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3">
+        <v>400</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>500</v>
+      </c>
+      <c r="R3">
+        <v>100</v>
+      </c>
+      <c r="S3" t="s">
         <v>25</v>
       </c>
-      <c r="F3">
-        <v>200</v>
-      </c>
-      <c r="G3">
-        <v>400</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>8</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>500</v>
-      </c>
-      <c r="Q3">
-        <v>100</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="U3" t="s">
+      <c r="W3" t="s">
         <v>33</v>
       </c>
-      <c r="V3" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
+      <c r="X3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
+      <c r="B4" t="s">
+        <v>34</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>300</v>
       </c>
       <c r="H4">
+        <v>300</v>
+      </c>
+      <c r="I4">
         <v>6</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>8</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>4</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
         <v>0</v>
       </c>
@@ -1356,36 +1358,39 @@
         <v>0</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>500</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>100</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
         <v>36</v>
       </c>
-      <c r="U4" t="s">
+      <c r="W4" t="s">
         <v>37</v>
       </c>
-      <c r="V4" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" t="s">
-        <v>30</v>
+      <c r="X4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
+      <c r="B5" t="s">
+        <v>38</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1394,29 +1399,29 @@
         <v>1</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>20</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>600</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>100</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
       </c>
       <c r="I5">
         <v>8</v>
       </c>
       <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
         <v>7</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
         <v>0</v>
       </c>
@@ -1427,20 +1432,22 @@
         <v>0</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>20</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1"/>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>39</v>
+      </c>
+      <c r="V5" t="s">
         <v>40</v>
-      </c>
-      <c r="U5" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/TitanSiege/Data/Excel/NPC配置表.xlsx
+++ b/TitanSiege/Data/Excel/NPC配置表.xlsx
@@ -1393,7 +1393,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>1</v>
